--- a/SaidaRPA/Excel/status-distribuidora_01-02-2026_28-02-2026.xlsx
+++ b/SaidaRPA/Excel/status-distribuidora_01-02-2026_28-02-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -486,26 +486,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CEA</t>
+          <t>CEEE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -516,11 +516,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Análise</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -531,22 +531,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -576,32 +576,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -610,58 +610,58 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -670,97 +670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Análise</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Novo</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Análise</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
         <v>15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
